--- a/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0003T0006Z000C1N27_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0003T0006Z000C1N27_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>40.08418675011257</v>
+        <v>6.513680346893294</v>
       </c>
       <c r="D2" t="n">
-        <v>37.57869494560209</v>
+        <v>6.106537928660341</v>
       </c>
       <c r="E2" t="n">
-        <v>7.13718978788885</v>
+        <v>1.159793340531938</v>
       </c>
       <c r="F2" t="n">
-        <v>8.381239716055005</v>
+        <v>1.361951453858938</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>36.82587947249607</v>
+        <v>5.984205414280612</v>
       </c>
       <c r="D3" t="n">
-        <v>33.76236117896876</v>
+        <v>5.486383691582423</v>
       </c>
       <c r="E3" t="n">
-        <v>7.13718978788885</v>
+        <v>1.159793340531938</v>
       </c>
       <c r="F3" t="n">
-        <v>8.381239716055005</v>
+        <v>1.361951453858938</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>36.67048099099028</v>
+        <v>5.958953161035921</v>
       </c>
       <c r="D4" t="n">
-        <v>37.09519417890509</v>
+        <v>6.027969054072077</v>
       </c>
       <c r="E4" t="n">
-        <v>7.13718978788885</v>
+        <v>1.159793340531938</v>
       </c>
       <c r="F4" t="n">
-        <v>8.381239716055005</v>
+        <v>1.361951453858938</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>41.06710375087547</v>
+        <v>6.673404359517264</v>
       </c>
       <c r="D5" t="n">
-        <v>37.5235446231743</v>
+        <v>6.097576001265824</v>
       </c>
       <c r="E5" t="n">
-        <v>7.13718978788885</v>
+        <v>1.159793340531938</v>
       </c>
       <c r="F5" t="n">
-        <v>8.381239716055005</v>
+        <v>1.361951453858938</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>33.86703172955424</v>
+        <v>5.503392656052564</v>
       </c>
       <c r="D6" t="n">
-        <v>30.1807031391168</v>
+        <v>4.904364260106481</v>
       </c>
       <c r="E6" t="n">
-        <v>7.13718978788885</v>
+        <v>1.159793340531938</v>
       </c>
       <c r="F6" t="n">
-        <v>8.381239716055005</v>
+        <v>1.361951453858938</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>34.93903542218183</v>
+        <v>5.677593256104548</v>
       </c>
       <c r="D7" t="n">
-        <v>20.12519685953756</v>
+        <v>3.270344489674854</v>
       </c>
       <c r="E7" t="n">
-        <v>7.13718978788885</v>
+        <v>1.159793340531938</v>
       </c>
       <c r="F7" t="n">
-        <v>8.381239716055005</v>
+        <v>1.361951453858938</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>41.00050273836799</v>
+        <v>6.662581694984799</v>
       </c>
       <c r="D8" t="n">
-        <v>37.54161855369306</v>
+        <v>6.100513014975123</v>
       </c>
       <c r="E8" t="n">
-        <v>7.13718978788885</v>
+        <v>1.159793340531938</v>
       </c>
       <c r="F8" t="n">
-        <v>8.381239716055005</v>
+        <v>1.361951453858938</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>35.05864794497819</v>
+        <v>5.697030291058956</v>
       </c>
       <c r="D9" t="n">
-        <v>26.0356335792865</v>
+        <v>4.230790456634057</v>
       </c>
       <c r="E9" t="n">
-        <v>7.13718978788885</v>
+        <v>1.159793340531938</v>
       </c>
       <c r="F9" t="n">
-        <v>8.381239716055005</v>
+        <v>1.361951453858938</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>27.43841822274848</v>
+        <v>4.458742961196629</v>
       </c>
       <c r="D10" t="n">
-        <v>20.395372907327</v>
+        <v>3.314248097440638</v>
       </c>
       <c r="E10" t="n">
-        <v>7.13718978788885</v>
+        <v>1.159793340531938</v>
       </c>
       <c r="F10" t="n">
-        <v>8.381239716055005</v>
+        <v>1.361951453858938</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>37.96386976733785</v>
+        <v>6.169128837192401</v>
       </c>
       <c r="D11" t="n">
-        <v>36.0367666779084</v>
+        <v>5.855974585160115</v>
       </c>
       <c r="E11" t="n">
-        <v>7.13718978788885</v>
+        <v>1.159793340531938</v>
       </c>
       <c r="F11" t="n">
-        <v>8.381239716055005</v>
+        <v>1.361951453858938</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>23.83682982272434</v>
+        <v>3.873484846192705</v>
       </c>
       <c r="D12" t="n">
-        <v>12.18987411340754</v>
+        <v>1.980854543428725</v>
       </c>
       <c r="E12" t="n">
-        <v>7.13718978788885</v>
+        <v>1.159793340531938</v>
       </c>
       <c r="F12" t="n">
-        <v>8.381239716055005</v>
+        <v>1.361951453858938</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>36.48490645526684</v>
+        <v>5.928797298980862</v>
       </c>
       <c r="D13" t="n">
-        <v>36.79234862729294</v>
+        <v>5.978756651935103</v>
       </c>
       <c r="E13" t="n">
-        <v>7.13718978788885</v>
+        <v>1.159793340531938</v>
       </c>
       <c r="F13" t="n">
-        <v>8.381239716055005</v>
+        <v>1.361951453858938</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>13.12931690887021</v>
+        <v>2.133513997691409</v>
       </c>
       <c r="D14" t="n">
-        <v>12.81407418661358</v>
+        <v>2.082287055324707</v>
       </c>
       <c r="E14" t="n">
-        <v>7.13718978788885</v>
+        <v>1.159793340531938</v>
       </c>
       <c r="F14" t="n">
-        <v>8.381239716055005</v>
+        <v>1.361951453858938</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>24.47805691728216</v>
+        <v>3.977684249058352</v>
       </c>
       <c r="D15" t="n">
-        <v>25.24787199656793</v>
+        <v>4.102779199442288</v>
       </c>
       <c r="E15" t="n">
-        <v>7.13718978788885</v>
+        <v>1.159793340531938</v>
       </c>
       <c r="F15" t="n">
-        <v>8.381239716055005</v>
+        <v>1.361951453858938</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>31.83511568943495</v>
+        <v>5.17320629953318</v>
       </c>
       <c r="D16" t="n">
-        <v>32.25893648481681</v>
+        <v>5.242077178782732</v>
       </c>
       <c r="E16" t="n">
-        <v>7.13718978788885</v>
+        <v>1.159793340531938</v>
       </c>
       <c r="F16" t="n">
-        <v>8.381239716055005</v>
+        <v>1.361951453858938</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>27.97370250288366</v>
+        <v>4.545726656718594</v>
       </c>
       <c r="D17" t="n">
-        <v>28.98311455723906</v>
+        <v>4.709756115551347</v>
       </c>
       <c r="E17" t="n">
-        <v>7.13718978788885</v>
+        <v>1.159793340531938</v>
       </c>
       <c r="F17" t="n">
-        <v>8.381239716055005</v>
+        <v>1.361951453858938</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>35.16085160203541</v>
+        <v>5.713638385330754</v>
       </c>
       <c r="D18" t="n">
-        <v>35.89477474856332</v>
+        <v>5.83290089664154</v>
       </c>
       <c r="E18" t="n">
-        <v>7.13718978788885</v>
+        <v>1.159793340531938</v>
       </c>
       <c r="F18" t="n">
-        <v>8.381239716055005</v>
+        <v>1.361951453858938</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
